--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250929_235129.xlsx
@@ -7884,7 +7884,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
